--- a/sensor_history.xlsx
+++ b/sensor_history.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -721,9 +721,32 @@
         <v>Spoilage / Toxic Risk</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15">
+        <v>1784723351421</v>
+      </c>
+      <c r="B15" t="str">
+        <v>22/07/2026, 5:59:11 PM</v>
+      </c>
+      <c r="C15" t="str">
+        <v>3.5</v>
+      </c>
+      <c r="D15">
+        <v>86</v>
+      </c>
+      <c r="E15">
+        <v>90</v>
+      </c>
+      <c r="F15" t="str">
+        <v>ON</v>
+      </c>
+      <c r="G15" t="str">
+        <v>Optimal Freshness</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G15"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sensor_history.xlsx
+++ b/sensor_history.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -744,9 +744,32 @@
         <v>Optimal Freshness</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16">
+        <v>1789789970902</v>
+      </c>
+      <c r="B16" t="str">
+        <v>19/09/2026, 9:22:50 AM</v>
+      </c>
+      <c r="C16" t="str">
+        <v>15.5</v>
+      </c>
+      <c r="D16">
+        <v>83</v>
+      </c>
+      <c r="E16">
+        <v>280</v>
+      </c>
+      <c r="F16" t="str">
+        <v>OFF</v>
+      </c>
+      <c r="G16" t="str">
+        <v>Spoilage / Toxic Risk</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G16"/>
   </ignoredErrors>
 </worksheet>
 </file>